--- a/Data/sorted_output.xlsx
+++ b/Data/sorted_output.xlsx
@@ -434,24 +434,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -586,7 +587,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -605,29 +606,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/742426015/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/287700029/detail.aspx</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>742426015</v>
+        <v>287700029</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Пальто оверсайз длинное весеннее</t>
+          <t>Пальто шерстяное натуральное</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4152.0</t>
+          <t>11685.0</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>the nana</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -637,31 +638,31 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62, 60, 50, 48, 46, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>the nana</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/236134</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
@@ -710,15 +711,15 @@
         <v>4.8</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176-182/54 рф, 176-182/52 рф, 170-176/50 рф, 170-176/48 рф, 170-176/46 рф, </t>
+          <t xml:space="preserve">178-184/56 рф, 176-182/54 рф, 176-182/52 рф, 170-176/48 рф, 170-176/46 рф, </t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -737,29 +738,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/287700029/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488387894/detail.aspx</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>287700029</v>
+        <v>488387894</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное натуральное</t>
+          <t>Пальто весна-осень макси в полоску</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11685.0</t>
+          <t>4306.0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -769,63 +770,63 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">48, 42, 44, 46, </t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/1304162</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/488387894/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/239833866/detail.aspx</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>488387894</v>
+        <v>239833866</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Пальто весна-осень макси в полоску</t>
+          <t>Пальто шерстяное демисезонное с воротником стойкой</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4306.0</t>
+          <t>8398.0</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>HANBIYKE</t>
+          <t>Coressi</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -839,27 +840,27 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>114</v>
+        <v>1847</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 42, 44, 46, </t>
+          <t xml:space="preserve">54, 52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>HANBIYKE</t>
+          <t>CORESSI</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1304162</t>
+          <t>https://www.wildberries.ru/seller/26796</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
@@ -869,27 +870,31 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/581383840/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/516341020/detail.aspx</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>581383840</v>
+        <v>516341020</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Длинное шерстяное пальто OVERSIZE на весну-осень</t>
+          <t>Пальто из шерсти альпака демисезонное</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7686.0</t>
+          <t>37321.0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>KROYYORK</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -897,7 +902,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, </t>
+          <t xml:space="preserve">фиолетовый, </t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -908,52 +913,52 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">56, 54, 52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>KROYYORK</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/25326</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/239833866/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/742426015/detail.aspx</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>239833866</v>
+        <v>742426015</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное с воротником стойкой</t>
+          <t>Пальто оверсайз длинное весеннее</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8398.0</t>
+          <t>4152.0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Coressi</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -963,63 +968,63 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1843</v>
+        <v>10</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54, 52, 50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">64, 62, 60, 54, 50, 48, 46, </t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>CORESSI</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/26796</t>
+          <t>https://www.wildberries.ru/seller/236134</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/310057846/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/500291585/detail.aspx</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>310057846</v>
+        <v>500291585</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Пальто женское весна-осень</t>
+          <t>Двубортное пальто из драпа с добавлением шерсти</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>4240.0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Alexander Serov</t>
+          <t>SELA</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1029,31 +1034,31 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">желтый, </t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1850</v>
+        <v>120</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60, 58, 56, 54, 40, 38, 52, 50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">42, 44, 50, 46, 48, </t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Alexander Serov GROUP</t>
+          <t>MELON FASHION GROUP</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1373064</t>
+          <t>https://www.wildberries.ru/seller/5862</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
@@ -1063,27 +1068,31 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/844840173/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/310057846/detail.aspx</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>844840173</v>
+        <v>310057846</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Осенне-весеннее шерстяное пальто с утяжкой на талии</t>
+          <t>Пальто женское весна-осень</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9113.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Serov</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -1091,61 +1100,65 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">желтый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>1852</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">60, 58, 56, 54, 40, 38, 52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>Alexander Serov GROUP</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/1373064</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/581260603/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/516995752/detail.aspx</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>581260603</v>
+        <v>516995752</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное весна-осень</t>
+          <t>Пальто осеннее длинное</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5809.0</t>
+          <t>9292.0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>MÁS</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -1157,31 +1170,31 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42, 44, 46, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>Mascota</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/1192923</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1253,29 +1266,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/500291585/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/775370787/detail.aspx</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>500291585</v>
+        <v>775370787</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Двубортное пальто из драпа с добавлением шерсти</t>
+          <t>Пальто пиджак приталенное</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4240.0</t>
+          <t>18273.0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>SELA</t>
+          <t>Eustera</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1285,31 +1298,31 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">желтый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42, 44, 50, 46, 48, </t>
+          <t xml:space="preserve">48-50, 46-48, 44-46, 42-44, </t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MELON FASHION GROUP</t>
+          <t>EUSTERA</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/5862</t>
+          <t>https://www.wildberries.ru/seller/867510</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
@@ -1319,27 +1332,31 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/319079863/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/257388507/detail.aspx</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>319079863</v>
+        <v>257388507</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Полупальто пиджак блейзер оверсайз короткое</t>
+          <t>Пальто демисезонное классика</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11793.0</t>
+          <t>10523.0</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Красный ананас</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -1347,63 +1364,63 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">синий, </t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>765</v>
+        <v>2610</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44-46, 48-50, 50-52, </t>
+          <t xml:space="preserve">176-182/54 рф, 176-182/52 рф, 170-176/50 рф, 170-176/48 рф, 170-176/46 рф, </t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>EverydayChic</t>
+          <t>Красный ананас</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/255231</t>
+          <t>https://www.wildberries.ru/seller/1316722</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/516995752/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/497508666/detail.aspx</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>516995752</v>
+        <v>497508666</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Пальто осеннее длинное</t>
+          <t>Пальто шерстяное короткое жакет</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9292.0</t>
+          <t>7610.0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>MÁS</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1413,65 +1430,61 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, </t>
+          <t xml:space="preserve">серый, белый, </t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46, 44, 42, </t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Lindo Gato</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/626100</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n">
         <v>4.9</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Mascota</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/1192923</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>4.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/257388507/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/319079863/detail.aspx</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>257388507</v>
+        <v>319079863</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Пальто демисезонное классика</t>
+          <t>Полупальто пиджак блейзер оверсайз короткое</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10523.0</t>
+          <t>10670.0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Красный ананас</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -1479,328 +1492,332 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">синий, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2609</v>
+        <v>765</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176-182/54 рф, 176-182/52 рф, 170-176/50 рф, 170-176/48 рф, 170-176/46 рф, </t>
+          <t xml:space="preserve">44-46, 48-50, </t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Красный ананас</t>
+          <t>EverydayChic</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1316722</t>
+          <t>https://www.wildberries.ru/seller/255231</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/497508666/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/277883751/detail.aspx</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>497508666</v>
+        <v>277883751</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное короткое жакет</t>
+          <t>Полупальто шерстяное</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7610.0</t>
+          <t>8141.0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, белый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46, 44, 42, </t>
+          <t xml:space="preserve">52, 50, 42, 48, 46, 44, </t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/626100</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/366417625/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/807004289/detail.aspx</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>366417625</v>
+        <v>807004289</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Короткое шерстяное пальто</t>
+          <t>Пальто из шерсти альпака демисезонное</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8926.0</t>
+          <t>48185.0</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>KROYYORK</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>пальто</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">голубой, </t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>MAISON DAVID</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>полупальто</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">бежевый, </t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="K18" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">48, 46, 44, 42, 54, 52, 50, </t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>KROYYORK</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/25326</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/481144243/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/287694148/detail.aspx</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>481144243</v>
+        <v>287694148</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное</t>
+          <t>Полупальто шерстяное</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22140.0</t>
+          <t>8926.0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>TRIUMF ST</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">бежевый, </t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52, 46, 42, </t>
+          <t xml:space="preserve">52, 50, 48, 46, 42, </t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>BERISHIN</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/312039</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/807004289/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/366417625/detail.aspx</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>807004289</v>
+        <v>366417625</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Пальто из шерсти альпака демисезонное</t>
+          <t>Короткое шерстяное пальто</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52565.0</t>
+          <t>8926.0</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>KROYYORK</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">голубой, </t>
+          <t xml:space="preserve">бежевый, </t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, 44, 42, 54, 52, 50, </t>
+          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>KROYYORK</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/25326</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/837907481/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/288989036/detail.aspx</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>837907481</v>
+        <v>288989036</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Осенне-весеннее шерстяное пальто с утяжкой на талии</t>
+          <t>Короткое шерстяное пальто</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8240.0</t>
+          <t>8533.0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1809,27 +1826,27 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
@@ -1839,34 +1856,34 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/277883751/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/789426062/detail.aspx</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>277883751</v>
+        <v>789426062</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Полупальто шерстяное</t>
+          <t>Пальто пиджак шерстяное</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8141.0</t>
+          <t>8201.0</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>LULLA</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>полупальто</t>
+          <t>пальто</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1875,31 +1892,31 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52, 50, 42, 48, 46, 44, </t>
+          <t xml:space="preserve">48, 46, 42, </t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>ИП Ковалева Ольга Алексеевна</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/31355</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="23">
@@ -1918,7 +1935,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12636.0</t>
+          <t>10389.0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1952,7 +1969,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1971,29 +1988,29 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/287694148/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/773082950/detail.aspx</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>287694148</v>
+        <v>773082950</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Полупальто шерстяное</t>
+          <t>Полупальто оверсайз из смесовой шерсти</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8926.0</t>
+          <t>9893.0</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>SELA</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2003,64 +2020,68 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="K24" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48, 46, </t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>MELON FASHION GROUP</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/5862</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/837898440/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/292873097/detail.aspx</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>837898440</v>
+        <v>292873097</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Осенне-весеннее шерстяное пальто с утяжкой на талии</t>
+          <t>Короткое шерстяное пальто</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8240.0</t>
+          <t>8141.0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2069,27 +2090,27 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
@@ -2099,31 +2120,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/304404090/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/319080049/detail.aspx</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>304404090</v>
+        <v>319080049</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Пальто длинное демисезонное</t>
+          <t>Полупальто пиджак блейзер оверсайз короткое</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13267.0</t>
+          <t>10670.0</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Befur</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -2131,31 +2148,31 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>132</v>
+        <v>765</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">44-46, 48-50, 50-52, </t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>BEFUR</t>
+          <t>EverydayChic</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/367672</t>
+          <t>https://www.wildberries.ru/seller/255231</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
@@ -2165,29 +2182,29 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/370477912/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/211881813/detail.aspx</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>370477912</v>
+        <v>211881813</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Женское пальто</t>
+          <t>Пальто короткое демисезонное на молнии, шерсть</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11685.0</t>
+          <t>10043.0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>Красный ананас</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2197,125 +2214,125 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">красный, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>9</v>
+        <v>2610</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52, 50, 48, 44, 46, </t>
+          <t xml:space="preserve">176-182/54 рф, 176-182/52 рф, 170-176/50 рф, 170-176/48 рф, </t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>Красный ананас</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/1316722</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/288989036/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/15323968/detail.aspx</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>288989036</v>
+        <v>15323968</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Короткое шерстяное пальто</t>
+          <t>Пальто весна-осень длинное</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8533.0</t>
+          <t>17690.0</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>Mmoda</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>полупальто</t>
+          <t>пальто</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">бежевый, желтый, </t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40-42, 48-50, 46-48, 44-46, 42-44, </t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Mmoda</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/37302</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
         <v>4.6</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>Rendez-Vous</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>4.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/581368864/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/560649727/detail.aspx</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>581368864</v>
+        <v>560649727</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное весна-осень</t>
+          <t>Пальто натуральная шерсть с мехом лисы</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4653.0</t>
+          <t>11597.0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
@@ -2325,61 +2342,65 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">40-42, </t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>ИП Безуглова А. И.</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/250047254</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/581403379/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/370477912/detail.aspx</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>581403379</v>
+        <v>370477912</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>пальто шерстяное длинное с жилеткой</t>
+          <t>Женское пальто</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6975.0</t>
+          <t>11685.0</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -2387,31 +2408,31 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">красный, </t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">52, 50, 48, 44, 46, </t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
@@ -2421,29 +2442,29 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/789426062/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/749357736/detail.aspx</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>789426062</v>
+        <v>749357736</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Пальто пиджак шерстяное</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8201.0</t>
+          <t>13643.0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>LULLA</t>
+          <t>BUTALABEL</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2453,45 +2474,45 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, 42, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>ИП Ковалева Ольга Алексеевна</t>
+          <t>Lumatex</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/31355</t>
+          <t>https://www.wildberries.ru/seller/146504</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/292873097/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/287694152/detail.aspx</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>292873097</v>
+        <v>287694152</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -2500,12 +2521,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>8141.0</t>
+          <t>8926.0</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2519,22 +2540,22 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">бежевый, </t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="K32" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46, 44, 52, 50, 48, 42, </t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>41</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>27</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2553,93 +2574,97 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/773082950/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/529987880/detail.aspx</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>773082950</v>
+        <v>529987880</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Полупальто оверсайз из смесовой шерсти</t>
+          <t>Пальто шерстяное весна-осень длинное двубортное</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>9893.0</t>
+          <t>7239.0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>SELA</t>
+          <t>Nataly Rik</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>полупальто</t>
+          <t>пальто</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, </t>
+          <t xml:space="preserve">42, 48, 44, 46, </t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MELON FASHION GROUP</t>
+          <t>ООО АФГ</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/5862</t>
+          <t>https://www.wildberries.ru/seller/1347707</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/581396640/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/146055032/detail.aspx</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>581396640</v>
+        <v>146055032</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>комплект из шерстяного полупальто и жилета</t>
+          <t>Пальто мужское длинное демисезонное оверсайз синее</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4963.0</t>
+          <t>5319.0</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>BYDAY</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -2647,31 +2672,31 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">синий, </t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>8</v>
+        <v>2610</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">52-182, 50-182, 46-182, 44-182, 54-170, 44-170, </t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>BYDAY WEAR</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/65778</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
@@ -2681,27 +2706,31 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/319080049/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/749357735/detail.aspx</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>319080049</v>
+        <v>749357735</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Полупальто пиджак блейзер оверсайз короткое</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>11232.0</t>
+          <t>13643.0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>BUTALABEL</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -2709,129 +2738,129 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>765</v>
+        <v>12</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44-46, 48-50, 50-52, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>EverydayChic</t>
+          <t>Lumatex</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/255231</t>
+          <t>https://www.wildberries.ru/seller/146504</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/287694152/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/481144273/detail.aspx</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>287694152</v>
+        <v>481144273</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Короткое шерстяное пальто</t>
+          <t>Пальто шерстяное демисезонное длинное шоколадное</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8926.0</t>
+          <t>22140.0</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>TRIUMF ST</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>полупальто</t>
+          <t>пальто</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46, 44, 52, 50, 48, 42, </t>
+          <t xml:space="preserve">50, 48, 46, </t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>BERISHIN</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/312039</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/211881813/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/505842316/detail.aspx</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>211881813</v>
+        <v>505842316</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Пальто короткое демисезонное на молнии, шерсть</t>
+          <t>Пальто демисезонное классика</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>10043.0</t>
+          <t>11203.0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Красный ананас</t>
+          <t>STPN - Wear</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2841,61 +2870,65 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2609</v>
+        <v>152</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176-182/54 рф, 176-182/52 рф, 170-176/50 рф, 170-176/48 рф, 170-176/46 рф, </t>
+          <t xml:space="preserve">54, 46, </t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Красный ананас</t>
+          <t>STPN</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1316722</t>
+          <t>https://www.wildberries.ru/seller/1167693</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/581260602/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/849729060/detail.aspx</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>581260602</v>
+        <v>849729060</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное весна-осень</t>
+          <t>Женское пальто</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6528.0</t>
+          <t>13905.0</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -2903,31 +2936,31 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">белый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42, 44, 46, </t>
+          <t xml:space="preserve">48, 46, 44, </t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Aura</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250060379</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
@@ -2937,29 +2970,29 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/505842316/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/723285888/detail.aspx</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>505842316</v>
+        <v>723285888</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Пальто демисезонное классика</t>
+          <t>Пальто весеннее длинное классическое</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11203.0</t>
+          <t>10228.0</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>STPN - Wear</t>
+          <t>Pudra Dress</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2969,31 +3002,31 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">белый, бежевый, </t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54, 48, 46, </t>
+          <t xml:space="preserve">50, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>STPN</t>
+          <t>Miss Nude &amp; Pudra Dress</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1167693</t>
+          <t>https://www.wildberries.ru/seller/82616</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
@@ -3003,29 +3036,29 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/775370787/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/107713204/detail.aspx</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>775370787</v>
+        <v>107713204</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Пальто пиджак приталенное</t>
+          <t>Пальто демисезонное прямое</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>18273.0</t>
+          <t>6356.0</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Eustera</t>
+          <t>5 LOVE</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3035,31 +3068,31 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">бежевый, </t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>101</v>
+        <v>340</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48-50, 46-48, 44-46, 42-44, </t>
+          <t xml:space="preserve">56, 42, 54, 52, 50, 48, 46, 44, </t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>EUSTERA</t>
+          <t>5 LOVE</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/867510</t>
+          <t>https://www.wildberries.ru/seller/705312</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
@@ -3069,29 +3102,29 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/15323968/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/330466210/detail.aspx</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>15323968</v>
+        <v>330466210</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Пальто весна-осень длинное</t>
+          <t>Пальто шерстяное натуральное</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>17690.0</t>
+          <t>12875.0</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Mmoda</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3101,61 +3134,65 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, желтый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40-42, 48-50, 46-48, 44-46, 42-44, </t>
+          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Mmoda</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/37302</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/560649727/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/304404090/detail.aspx</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>560649727</v>
+        <v>304404090</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Пальто натуральная шерсть с мехом лисы</t>
+          <t>Пальто длинное демисезонное</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>11597.0</t>
+          <t>10565.0</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Befur</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -3163,63 +3200,63 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40-42, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>ИП Безуглова А. И.</t>
+          <t>BEFUR</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250047254</t>
+          <t>https://www.wildberries.ru/seller/367672</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/481144273/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/770695812/detail.aspx</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>481144273</v>
+        <v>770695812</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное шоколадное</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>22140.0</t>
+          <t>15579.0</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>TRIUMF ST</t>
+          <t>Coressi</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3229,31 +3266,31 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>54</v>
+        <v>442</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 48, 46, </t>
+          <t xml:space="preserve">54, 52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>BERISHIN</t>
+          <t>CORESSI</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/312039</t>
+          <t>https://www.wildberries.ru/seller/26796</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
@@ -3263,29 +3300,29 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/749357736/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/225889315/detail.aspx</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>749357736</v>
+        <v>225889315</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное</t>
+          <t>Весеннее пальто в полоску длинное</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>7766.0</t>
+          <t>4036.0</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>BUTALABEL</t>
+          <t>NARRATIVE</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3295,35 +3332,35 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44-48, 48-52, </t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>АСТ Ретейл</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/35512</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n">
         <v>4.9</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>Lumatex</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/146504</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>4.8</v>
       </c>
     </row>
     <row r="45">
@@ -3368,15 +3405,15 @@
         <v>4.9</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, 44, 42, </t>
+          <t xml:space="preserve">48, 46, 42, </t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -3395,29 +3432,29 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/146055032/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/770729449/detail.aspx</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>146055032</v>
+        <v>770729449</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Пальто мужское длинное демисезонное оверсайз синее</t>
+          <t>Пальто короткое из натуральной шерсти</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>5319.0</t>
+          <t>8723.0</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>BYDAY</t>
+          <t>Suerte more</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3427,65 +3464,61 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">синий, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2609</v>
+        <v>28</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52-182, 50-182, 46-182, 44-182, 54-170, 44-170, </t>
+          <t xml:space="preserve">52, 50, 48, 46, </t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>BYDAY WEAR</t>
+          <t>Suerte more</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/65778</t>
+          <t>https://www.wildberries.ru/seller/250020687</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/749357735/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/805106976/detail.aspx</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>749357735</v>
+        <v>805106976</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное</t>
+          <t>Пальто с шарфом 100% шерсть короткое большие размеры</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>7976.0</t>
+          <t>14288.0</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>BUTALABEL</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -3493,31 +3526,31 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, серый, </t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">48-50, 50-52, 54-56, </t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Lumatex</t>
+          <t>MATORINA</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/146504</t>
+          <t>https://www.wildberries.ru/seller/116400</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
@@ -3527,29 +3560,29 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/330466210/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/771425157/detail.aspx</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>330466210</v>
+        <v>771425157</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное натуральное</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>12875.0</t>
+          <t>13643.0</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>BUTALABEL</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3559,63 +3592,63 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>Lumatex</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/146504</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/529987880/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/497552528/detail.aspx</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>529987880</v>
+        <v>497552528</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное весна-осень длинное двубортное</t>
+          <t>Пальто шерстяное короткое жакет</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>7239.0</t>
+          <t>7265.0</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Nataly Rik</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3625,129 +3658,125 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42, 48, 44, 46, </t>
+          <t xml:space="preserve">46, 42, 44, </t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>ООО АФГ</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1347707</t>
+          <t>https://www.wildberries.ru/seller/626100</t>
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/723285888/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/493577428/detail.aspx</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>723285888</v>
+        <v>493577428</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Пальто весеннее длинное классическое</t>
+          <t>Весеннее шерстяное пальто на молнии</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>10228.0</t>
+          <t>6150.0</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Pudra Dress</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">белый, бежевый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 46, 44, 42, </t>
+          <t xml:space="preserve">52, 50, </t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Miss Nude &amp; Pudra Dress</t>
+          <t>Уютмаркет</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/82616</t>
+          <t>https://www.wildberries.ru/seller/250001823</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/770695812/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/497508664/detail.aspx</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>770695812</v>
+        <v>497508664</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное</t>
+          <t>Пальто шерстяное короткое жакет</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>15579.0</t>
+          <t>7610.0</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Coressi</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3757,63 +3786,63 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">зеленый, серый, коричневый, </t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>442</v>
+        <v>53</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54, 52, 50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">46, 44, 42, </t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>CORESSI</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/26796</t>
+          <t>https://www.wildberries.ru/seller/626100</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/797007604/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/775379354/detail.aspx</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>797007604</v>
+        <v>775379354</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Пальто драповое приталенное с отложным воротником</t>
+          <t>Пальто пиджак приталенное</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>7242.0</t>
+          <t>18273.0</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Befree</t>
+          <t>Eustera</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3827,27 +3856,27 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46, 42, </t>
+          <t xml:space="preserve">48-50, 42-44, 44-46, 46-48, </t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MELON FASHION GROUP</t>
+          <t>EUSTERA</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/5862</t>
+          <t>https://www.wildberries.ru/seller/867510</t>
         </is>
       </c>
       <c r="P52" s="2" t="n">
@@ -3857,97 +3886,93 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/225889315/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/836686592/detail.aspx</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>225889315</v>
+        <v>836686592</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Весеннее пальто в полоску длинное</t>
+          <t>Женское полупальто</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>4036.0</t>
+          <t>8366.0</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>NARRATIVE</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52, 48, 46, </t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
         <v>4.7</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44-48, 48-52, </t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>АСТ Ретейл</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/35512</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>4.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/107713204/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/311905357/detail.aspx</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>107713204</v>
+        <v>311905357</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Пальто демисезонное прямое</t>
+          <t>Полупальто пиджак блейзер оверсайз короткое</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>6356.0</t>
+          <t>11137.0</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>5 LOVE</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -3955,63 +3980,63 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>340</v>
+        <v>765</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56, 42, 54, 52, 50, 48, 46, 44, </t>
+          <t xml:space="preserve">44-46, 48-50, 50-52, </t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>5 LOVE</t>
+          <t>EverydayChic</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/705312</t>
+          <t>https://www.wildberries.ru/seller/255231</t>
         </is>
       </c>
       <c r="P54" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/775379354/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/526167031/detail.aspx</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>775379354</v>
+        <v>526167031</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Пальто пиджак приталенное</t>
+          <t>Пальто женское весна-осень демисезонное</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>18273.0</t>
+          <t>3955.0</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Eustera</t>
+          <t>LiBrand</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4021,63 +4046,63 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, серый, </t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48-50, 42-44, 44-46, 46-48, </t>
+          <t xml:space="preserve">48, 46, </t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>EUSTERA</t>
+          <t>LiBrand</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/867510</t>
+          <t>https://www.wildberries.ru/seller/4162994</t>
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/257303252/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/770719296/detail.aspx</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>257303252</v>
+        <v>770719296</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное с воротником стойкой</t>
+          <t>Пальто шерстяное демисезонное</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>8665.0</t>
+          <t>8723.0</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Coressi</t>
+          <t>Suerte more</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4087,63 +4112,63 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52, 50, 48, 46, </t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Suerte more</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250020687</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
         <v>4.9</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>469</v>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52, 48, 42, </t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>CORESSI</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/26796</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>4.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/771425157/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/346320940/detail.aspx</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>771425157</v>
+        <v>346320940</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное</t>
+          <t>Пальто шерстяное натуральное</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>7976.0</t>
+          <t>11122.0</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>BUTALABEL</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4153,63 +4178,63 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">бежевый, </t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
         <v>4.6</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">46, </t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Lumatex</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/146504</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/329473994/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/825019950/detail.aspx</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>329473994</v>
+        <v>825019950</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Пальто короткое приталенное весна</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>9582.0</t>
+          <t>13643.0</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Befur</t>
+          <t>BUTALABEL</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4219,14 +4244,14 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -4234,82 +4259,82 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>BEFUR</t>
+          <t>Lumatex</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/367672</t>
+          <t>https://www.wildberries.ru/seller/146504</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/836686592/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/771001071/detail.aspx</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>836686592</v>
+        <v>771001071</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Женское полупальто</t>
+          <t>Пальто демисезонное</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>8366.0</t>
+          <t>4746.0</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>SerpikovaNS</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>пальто</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">коричневый, </t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K59" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>MAISON DAVID</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>полупальто</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">черный, </t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52, 48, 46, </t>
+          <t xml:space="preserve">48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>SerpikovaNS</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/1402110</t>
         </is>
       </c>
       <c r="P59" s="2" t="n">
@@ -4319,31 +4344,27 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/526167031/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/541448913/detail.aspx</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>526167031</v>
+        <v>541448913</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Пальто женское весна-осень демисезонное</t>
+          <t>Пальто шерстяное весна-осень</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>3955.0</t>
+          <t>9405.0</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>LiBrand</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -4351,64 +4372,68 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, серый, </t>
+          <t xml:space="preserve">бежевый, </t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, 44, </t>
+          <t xml:space="preserve">44, 46, </t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>LiBrand</t>
+          <t>POLARIX</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/4162994</t>
+          <t>https://www.wildberries.ru/seller/250000954</t>
         </is>
       </c>
       <c r="P60" s="2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/493577428/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/911457576/detail.aspx</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>493577428</v>
+        <v>911457576</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Весеннее шерстяное пальто на молнии</t>
+          <t>Женское пальто</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>6150.0</t>
+          <t>12865.0</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>полупальто</t>
+          <t>пальто</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4417,57 +4442,61 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46, </t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
         <v>4.7</v>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52, 50, </t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>Уютмаркет</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/250001823</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>4.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/595049394/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/329473994/detail.aspx</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>595049394</v>
+        <v>329473994</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное весна-осень</t>
+          <t>Пальто короткое приталенное весна</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>6394.0</t>
+          <t>9582.0</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Befur</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -4475,31 +4504,31 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>POLARIX</t>
+          <t>BEFUR</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250000954</t>
+          <t>https://www.wildberries.ru/seller/367672</t>
         </is>
       </c>
       <c r="P62" s="2" t="n">
@@ -4509,29 +4538,29 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/497508664/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/182534928/detail.aspx</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>497508664</v>
+        <v>182534928</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное короткое жакет</t>
+          <t>Пальто</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>7610.0</t>
+          <t>4235.0</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>THOMAS MUNZ</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4541,88 +4570,88 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">зеленый, серый, коричневый, </t>
+          <t xml:space="preserve">желтый, </t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46, 44, 42, </t>
+          <t xml:space="preserve">46/164-170, 48/170, </t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>MUNZ GROUP</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/626100</t>
+          <t>https://www.wildberries.ru/seller/27600</t>
         </is>
       </c>
       <c r="P63" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/346320940/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/834814797/detail.aspx</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>346320940</v>
+        <v>834814797</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное натуральное</t>
+          <t>Женское пальто</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>11122.0</t>
+          <t>14081.0</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>пальто</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">серый, </t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>MAISON DAVID</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">бежевый, </t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="K64" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 46, </t>
+          <t xml:space="preserve">48, 46, </t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -4641,31 +4670,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/771001071/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/595049394/detail.aspx</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>771001071</v>
+        <v>595049394</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Пальто демисезонное</t>
+          <t>Пальто шерстяное весна-осень</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>4746.0</t>
+          <t>6394.0</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>SerpikovaNS</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -4673,63 +4698,63 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>5</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, 44, 42, </t>
+          <t xml:space="preserve">42, </t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>SerpikovaNS</t>
+          <t>POLARIX</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1402110</t>
+          <t>https://www.wildberries.ru/seller/250000954</t>
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/192213044/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/163566992/detail.aspx</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>192213044</v>
+        <v>163566992</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Пальто классическое теплое на весну</t>
+          <t>Пальто весеннее шерстяное кимоно без подклада оверсайз</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>5728.0</t>
+          <t>7968.0</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>milidi</t>
+          <t>VESHALKA</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4739,63 +4764,63 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">розовый, бежевый, коричневый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>254</v>
+        <v>378</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54-62, </t>
+          <t xml:space="preserve">50-52, 46-48, 42-44, </t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Магазин одежды бохо</t>
+          <t>VESHALKA</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/61696</t>
+          <t>https://www.wildberries.ru/seller/1287074</t>
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/197262900/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/312616259/detail.aspx</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>197262900</v>
+        <v>312616259</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Пальто женское демисезонное оверсайз теплое длинное</t>
+          <t>Женское пальто</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>7862.0</t>
+          <t>12494.0</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>EURYDIKE</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4809,57 +4834,61 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>508</v>
+        <v>24</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">48, 46, 44, </t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Eurydike</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/3971567</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/805106976/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/333388543/detail.aspx</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>805106976</v>
+        <v>333388543</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Пальто с шарфом 100% шерсть короткое большие размеры</t>
+          <t>Женское пальто</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>14288.0</t>
+          <t>11685.0</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -4867,61 +4896,65 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, серый, </t>
+          <t xml:space="preserve">бежевый, </t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48-50, 50-52, 54-56, </t>
+          <t xml:space="preserve">50, 46, 44, 48, </t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MATORINA</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/116400</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/541448913/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488387892/detail.aspx</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>541448913</v>
+        <v>488387892</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное весна-осень</t>
+          <t>Пальто длинное оверсайз весна-осень</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>9405.0</t>
+          <t>4251.0</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>HANBIYKE</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -4929,63 +4962,63 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">48, 42, 44, 46, </t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>POLARIX</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250000954</t>
+          <t>https://www.wildberries.ru/seller/1304162</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/312616259/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/297712814/detail.aspx</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>312616259</v>
+        <v>297712814</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Женское пальто</t>
+          <t>Пальто шерстяное длинное без подкладки</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>12494.0</t>
+          <t>28643.0</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>OKSANA UTOVA BRAND</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4995,31 +5028,31 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, 44, </t>
+          <t xml:space="preserve">64-66, 58-60, 42-48, 54-56, 60-62, </t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>OKSANA UTOVA BRAND</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/814984</t>
         </is>
       </c>
       <c r="P70" s="2" t="n">
@@ -5029,59 +5062,63 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/311905357/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/914196635/detail.aspx</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>311905357</v>
+        <v>914196635</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Полупальто пиджак блейзер оверсайз короткое</t>
+          <t>Женское полупальто</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>11723.0</t>
+          <t>6711.0</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>765</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44-46, 48-50, 50-52, </t>
+          <t xml:space="preserve">46, </t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>EverydayChic</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/255231</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P71" s="2" t="n">
@@ -5091,29 +5128,29 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/770729449/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/493989817/detail.aspx</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>770729449</v>
+        <v>493989817</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Пальто короткое из натуральной шерсти</t>
+          <t>Пальто зимнее длинное с люрексом без пояса натуральный мех</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>8723.0</t>
+          <t>17292.0</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Suerte more</t>
+          <t>Элегант</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5123,63 +5160,63 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52, 50, 48, 46, </t>
+          <t xml:space="preserve">46, 48, 64, 62, 60, 58, 54, 52, 50, </t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Suerte more</t>
+          <t>Элегант</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250020687</t>
+          <t>https://www.wildberries.ru/seller/40236</t>
         </is>
       </c>
       <c r="P72" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/911457576/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/197262900/detail.aspx</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>911457576</v>
+        <v>197262900</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Женское пальто</t>
+          <t>Пальто женское демисезонное оверсайз теплое длинное</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>12865.0</t>
+          <t>7862.0</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>EURYDIKE</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5193,59 +5230,59 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>508</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 46, </t>
+          <t xml:space="preserve">52, 50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>Eurydike</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/3971567</t>
         </is>
       </c>
       <c r="P73" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/825019950/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/287755147/detail.aspx</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>825019950</v>
+        <v>287755147</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное</t>
+          <t>Пальто двубортное драповое с шерстью демисезонное</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>13643.0</t>
+          <t>3789.0</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>BUTALABEL</t>
+          <t>Befree</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5255,31 +5292,31 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
+          <t xml:space="preserve">48, 46, </t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Lumatex</t>
+          <t>MELON FASHION GROUP</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/146504</t>
+          <t>https://www.wildberries.ru/seller/5862</t>
         </is>
       </c>
       <c r="P74" s="2" t="n">
@@ -5289,95 +5326,95 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/497552528/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/874597322/detail.aspx</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>497552528</v>
+        <v>874597322</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное короткое жакет</t>
+          <t>Пальто женское демисезонное шерстяное классическое с поясом</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>7265.0</t>
+          <t>5328.0</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>Milens</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>пальто</t>
+          <t>полупальто</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">голубой, </t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46, 42, 44, </t>
+          <t xml:space="preserve">48, 46, 44, 42, 40, </t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>Milens</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/626100</t>
+          <t>https://www.wildberries.ru/seller/109326</t>
         </is>
       </c>
       <c r="P75" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/333388543/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488387893/detail.aspx</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>333388543</v>
+        <v>488387893</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Женское пальто</t>
+          <t>Пальто весна-осень макси в полоску</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>11685.0</t>
+          <t>4306.0</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5387,63 +5424,63 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, </t>
+          <t xml:space="preserve">синий, </t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 46, 44, 42, 48, </t>
+          <t xml:space="preserve">48, 42, 44, 46, </t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/1304162</t>
         </is>
       </c>
       <c r="P76" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/496842835/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/482254030/detail.aspx</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>496842835</v>
+        <v>482254030</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Пальто оверсайз длинное драповое с поясом</t>
+          <t>Пальто пиджак оверсайз серое женское из 100% шерсти</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>5305.0</t>
+          <t>3955.0</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Befree</t>
+          <t>Harizmic</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -5453,63 +5490,63 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 48, 46, 44, </t>
+          <t xml:space="preserve">38-44, </t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MELON FASHION GROUP</t>
+          <t>Harizmic</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/5862</t>
+          <t>https://www.wildberries.ru/seller/363171</t>
         </is>
       </c>
       <c r="P77" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/849729060/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/502427212/detail.aspx</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>849729060</v>
+        <v>502427212</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Женское пальто</t>
+          <t>Пальто демисезонное</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>13905.0</t>
+          <t>4746.0</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>SerpikovaNS</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5519,31 +5556,31 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50, 48, 46, 44, </t>
+          <t xml:space="preserve">48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Rendez-Vous</t>
+          <t>SerpikovaNS</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/1402110</t>
         </is>
       </c>
       <c r="P78" s="2" t="n">
@@ -5553,29 +5590,29 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/182534928/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/324425182/detail.aspx</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>182534928</v>
+        <v>324425182</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Пальто</t>
+          <t>Пальто шерстяное натуральное</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>4235.0</t>
+          <t>12206.0</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>THOMAS MUNZ</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5585,63 +5622,63 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">желтый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44/164, 46/164-170, 48/170, </t>
+          <t xml:space="preserve">52, 50, 46, 42, 48, 44, </t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MUNZ GROUP</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/27600</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/502427212/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/723231379/detail.aspx</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>502427212</v>
+        <v>723231379</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Пальто демисезонное</t>
+          <t>Пальто весеннее длинное классическое</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4746.0</t>
+          <t>10228.0</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>SerpikovaNS</t>
+          <t>Pudra Dress</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5651,31 +5688,31 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, 44, 42, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>SerpikovaNS</t>
+          <t>Miss Nude &amp; Pudra Dress</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1402110</t>
+          <t>https://www.wildberries.ru/seller/82616</t>
         </is>
       </c>
       <c r="P80" s="2" t="n">
@@ -5685,29 +5722,29 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/488387892/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/826929939/detail.aspx</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>488387892</v>
+        <v>826929939</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Пальто длинное оверсайз весна-осень</t>
+          <t>Пальто демисезонное оверсайз</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>4251.0</t>
+          <t>2648.0</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>HANBIYKE</t>
+          <t>YFH</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -5717,63 +5754,63 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">коричневый, </t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 42, 44, 46, </t>
+          <t xml:space="preserve">48-50, </t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>HANBIYKE</t>
+          <t>Королва</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1304162</t>
+          <t>https://www.wildberries.ru/seller/250033719</t>
         </is>
       </c>
       <c r="P81" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/493989817/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/267900794/detail.aspx</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>493989817</v>
+        <v>267900794</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Пальто зимнее длинное с люрексом без пояса натуральный мех</t>
+          <t>Пальто шерстяное длинное без подкладки</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>17292.0</t>
+          <t>28643.0</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Элегант</t>
+          <t>OKSANA UTOVA BRAND</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5783,31 +5820,31 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">черный, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46, 48, 64, 62, 60, 58, 54, 52, 50, </t>
+          <t xml:space="preserve">64-66, 60-62, 58-60, 42-48, 50-52, 54-56, </t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Элегант</t>
+          <t>OKSANA UTOVA BRAND</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/40236</t>
+          <t>https://www.wildberries.ru/seller/814984</t>
         </is>
       </c>
       <c r="P82" s="2" t="n">
@@ -5817,25 +5854,25 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/799262135/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/544914036/detail.aspx</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>799262135</v>
+        <v>544914036</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>пальто шерстяное длинное с жилеткой</t>
+          <t>Пальто шерстяное весна-осень</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>4695.0</t>
+          <t>7154.0</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
@@ -5849,127 +5886,123 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44, 46, </t>
+          <t xml:space="preserve">42, 44, 46, </t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>YUN YUE</t>
+          <t>POLARIX</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/250100879</t>
+          <t>https://www.wildberries.ru/seller/250000954</t>
         </is>
       </c>
       <c r="P83" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/874597322/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/865214901/detail.aspx</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>874597322</v>
+        <v>865214901</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Пальто женское демисезонное шерстяное классическое с поясом</t>
+          <t>Женское пальто</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>5328.0</t>
+          <t>11265.0</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Milens</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>полупальто</t>
+          <t>пальто</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">голубой, </t>
+          <t xml:space="preserve">розовый, </t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48, 46, 44, 42, 40, </t>
+          <t xml:space="preserve">48, 46, 42, </t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Milens</t>
+          <t>Rendez-Vous</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/109326</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="P84" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/297712814/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/537146660/detail.aspx</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>297712814</v>
+        <v>537146660</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное длинное без подкладки</t>
+          <t>Пальто шерстяное весна-осень</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>28643.0</t>
+          <t>8121.0</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>OKSANA UTOVA BRAND</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -5977,65 +6010,61 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">коричневый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44, 46, </t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>POLARIX</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250000954</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="n">
         <v>4.8</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64-66, 58-60, 42-48, 54-56, 60-62, </t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>OKSANA UTOVA BRAND</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/814984</t>
-        </is>
-      </c>
-      <c r="P85" s="2" t="n">
-        <v>4.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/15323969/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/543691598/detail.aspx</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>15323969</v>
+        <v>543691598</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Пальто весна-осень длинное</t>
+          <t>пальто шерстяное длинное с жилеткой</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>15233.0</t>
+          <t>5709.0</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Mmoda</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>пальто</t>
@@ -6043,63 +6072,63 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">бежевый, коричневый, </t>
+          <t xml:space="preserve">серый, </t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>204</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40-42, 44-46, </t>
+          <t xml:space="preserve">46, </t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Mmoda</t>
+          <t>POLARIX</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/37302</t>
+          <t>https://www.wildberries.ru/seller/250000954</t>
         </is>
       </c>
       <c r="P86" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/267900794/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/723288591/detail.aspx</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>267900794</v>
+        <v>723288591</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное длинное без подкладки</t>
+          <t>Пальто весеннее длинное классическое</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>28643.0</t>
+          <t>10663.0</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>OKSANA UTOVA BRAND</t>
+          <t>Pudra Dress</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6109,31 +6138,31 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">черный, </t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64-66, 60-62, 58-60, 42-48, 50-52, 54-56, </t>
+          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>OKSANA UTOVA BRAND</t>
+          <t>Miss Nude &amp; Pudra Dress</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/814984</t>
+          <t>https://www.wildberries.ru/seller/82616</t>
         </is>
       </c>
       <c r="P87" s="2" t="n">
@@ -6143,29 +6172,29 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/505531759/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/172909482/detail.aspx</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>505531759</v>
+        <v>172909482</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Двубортное пальто из драпа с содержанием шерсти</t>
+          <t>Пальто из шерсти альпака демисезонное двубортное</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>5895.0</t>
+          <t>36019.0</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>SELA</t>
+          <t>KROYYORK</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6175,621 +6204,35 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">серый, </t>
+          <t xml:space="preserve">бежевый, </t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46, </t>
+          <t xml:space="preserve">54-56, 52-54, 50-52, 48-50, </t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MELON FASHION GROUP</t>
+          <t>KROYYORK</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/5862</t>
+          <t>https://www.wildberries.ru/seller/25326</t>
         </is>
       </c>
       <c r="P88" s="2" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/425442519/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="n">
-        <v>425442519</v>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Двубортное пальто из шерсти</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>8877.0</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>LOVE REPUBLIC</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">красный, </t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44/170, </t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N89" s="2" t="inlineStr">
-        <is>
-          <t>MELON FASHION GROUP</t>
-        </is>
-      </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/5862</t>
-        </is>
-      </c>
-      <c r="P89" s="2" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/488387893/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="n">
-        <v>488387893</v>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Пальто весна-осень макси в полоску</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>4306.0</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>HANBIYKE</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">синий, </t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48, 42, 44, 46, </t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>HANBIYKE</t>
-        </is>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/1304162</t>
-        </is>
-      </c>
-      <c r="P90" s="2" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/537146660/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="n">
-        <v>537146660</v>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Пальто шерстяное весна-осень</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>8121.0</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">серый, </t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="n">
         <v>4.6</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44, 46, </t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>POLARIX</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/250000954</t>
-        </is>
-      </c>
-      <c r="P91" s="2" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/482254030/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="n">
-        <v>482254030</v>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Пальто пиджак оверсайз серое женское из 100% шерсти</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>3955.0</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Harizmic</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">серый, </t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38-44, </t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="N92" s="2" t="inlineStr">
-        <is>
-          <t>Harizmic</t>
-        </is>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/363171</t>
-        </is>
-      </c>
-      <c r="P92" s="2" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/914196635/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="n">
-        <v>914196635</v>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Женское полупальто</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>6711.0</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>MAISON DAVID</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>полупальто</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">коричневый, </t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46, </t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N93" s="2" t="inlineStr">
-        <is>
-          <t>Rendez-Vous</t>
-        </is>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
-        </is>
-      </c>
-      <c r="P93" s="2" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/842654533/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="n">
-        <v>842654533</v>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Мужское пальто</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>8338.0</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>MAISON DAVID</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">синий, </t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54, 52, 50, 48, </t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="N94" s="2" t="inlineStr">
-        <is>
-          <t>Rendez-Vous</t>
-        </is>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
-        </is>
-      </c>
-      <c r="P94" s="2" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/543691598/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="n">
-        <v>543691598</v>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>пальто шерстяное длинное с жилеткой</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>5709.0</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">серый, </t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46, </t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>POLARIX</t>
-        </is>
-      </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/250000954</t>
-        </is>
-      </c>
-      <c r="P95" s="2" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/723288591/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="n">
-        <v>723288591</v>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Пальто весеннее длинное классическое</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>10663.0</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Pudra Dress</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">черный, </t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="N96" s="2" t="inlineStr">
-        <is>
-          <t>Miss Nude &amp; Pudra Dress</t>
-        </is>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/82616</t>
-        </is>
-      </c>
-      <c r="P96" s="2" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/723231379/detail.aspx</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="n">
-        <v>723231379</v>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Пальто весеннее длинное классическое</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>10228.0</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Pudra Dress</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>пальто</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">коричневый, </t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50, 48, 46, 44, 42, </t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>Miss Nude &amp; Pudra Dress</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/seller/82616</t>
-        </is>
-      </c>
-      <c r="P97" s="2" t="n">
-        <v>4.7</v>
       </c>
     </row>
   </sheetData>
